--- a/3rd_SEMESTER/Statistics/Linear-Regression/Linear-Regression.xlsx
+++ b/3rd_SEMESTER/Statistics/Linear-Regression/Linear-Regression.xlsx
@@ -205,18 +205,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
@@ -561,10 +560,10 @@
       <c r="B4">
         <v>2.9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -573,10 +572,10 @@
       <c r="B5">
         <v>3.8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>0.99916447899415772</v>
       </c>
     </row>
@@ -587,10 +586,10 @@
       <c r="B6">
         <v>4.5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>0.99832965608366675</v>
       </c>
     </row>
@@ -601,10 +600,10 @@
       <c r="B7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>0.99812086309412518</v>
       </c>
     </row>
@@ -615,10 +614,10 @@
       <c r="B8">
         <v>5.8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>9.0117768066081835E-2</v>
       </c>
     </row>
@@ -629,10 +628,10 @@
       <c r="B9">
         <v>6.3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>10</v>
       </c>
     </row>
@@ -662,72 +661,70 @@
       <c r="B12">
         <v>8.5</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>38.831030303030303</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>38.831030303030303</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13">
         <v>4781.4328358208968</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13">
         <v>2.1299629442675629E-12</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>6.4969696969696955E-2</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>8.1212121212121194E-3</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>9</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <v>38.896000000000001</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="17" spans="4:12" x14ac:dyDescent="0.3">
       <c r="E17" t="s">
